--- a/results/errors/residuals_stats.xlsx
+++ b/results/errors/residuals_stats.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.4071903709226694</v>
+        <v>-0.1707294536750584</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07167570330029119</v>
+        <v>0.06821902511075469</v>
       </c>
     </row>
     <row r="3">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.1870547685147394</v>
+        <v>-0.227823451471435</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06326858087736695</v>
+        <v>0.05420868590638327</v>
       </c>
     </row>
     <row r="4">
@@ -518,10 +518,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.09822558890989119</v>
+        <v>-0.1265317751090794</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07096087336278739</v>
+        <v>0.06901538823188524</v>
       </c>
     </row>
     <row r="5">
@@ -541,10 +541,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.470964777832612</v>
+        <v>-0.1527616931121617</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07732524049328046</v>
+        <v>0.08065390497604527</v>
       </c>
     </row>
     <row r="6">
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.09180090359062647</v>
+        <v>-0.1680943720659683</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07163474188778729</v>
+        <v>0.06200653232142157</v>
       </c>
     </row>
     <row r="7">
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.825681019192323</v>
+        <v>-1.347116458778962</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1657137147064501</v>
+        <v>0.08406752988752667</v>
       </c>
     </row>
     <row r="8">
@@ -711,7 +711,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fertilizer consumption (% of fertilizer production)</t>
+          <t>Cereal yield (kg per hectare)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -725,16 +725,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-50.79741940984609</v>
+        <v>72.55377604166642</v>
       </c>
       <c r="E13" t="n">
-        <v>44.91033702003426</v>
+        <v>337.8101647926924</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Fertilizer consumption (% of fertilizer production)</t>
+          <t>Cereal yield (kg per hectare)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -748,16 +748,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-71.03285108098866</v>
+        <v>-102.492797851563</v>
       </c>
       <c r="E14" t="n">
-        <v>22.2374871443471</v>
+        <v>344.1967708716385</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Fertilizer consumption (% of fertilizer production)</t>
+          <t>Cereal yield (kg per hectare)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -771,16 +771,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-73.47167096624257</v>
+        <v>-119.3868977864586</v>
       </c>
       <c r="E15" t="n">
-        <v>8.521519470986854</v>
+        <v>352.7298430479694</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Fertilizer consumption (% of fertilizer production)</t>
+          <t>Cereal yield (kg per hectare)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -794,16 +794,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-70.48490033635976</v>
+        <v>-33.17229817708358</v>
       </c>
       <c r="E16" t="n">
-        <v>25.33689662365463</v>
+        <v>353.036953051361</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Fertilizer consumption (% of fertilizer production)</t>
+          <t>Cereal yield (kg per hectare)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -817,32 +817,308 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-77.18818173894765</v>
+        <v>-144.3757324218755</v>
       </c>
       <c r="E17" t="n">
-        <v>35.76411924524427</v>
+        <v>354.4326368779683</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Cereal yield (kg per hectare)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>TPE_step_aug</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-87.2544108072919</v>
+      </c>
+      <c r="E18" t="n">
+        <v>354.0006234251761</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Employment in agriculture (% of total employment)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Random_jitter_aug</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.2976835713699069</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.1401521899295723</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Employment in agriculture (% of total employment)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Random_orig</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.1320322499587741</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.09499714155921102</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Employment in agriculture (% of total employment)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Random_step_aug</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.1210509286239352</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.08998772879370809</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Employment in agriculture (% of total employment)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>TPE_jitter_aug</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.2139017329528536</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.02975115557440877</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Employment in agriculture (% of total employment)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>TPE_orig</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-0.03431830266263147</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.05706355353125692</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Employment in agriculture (% of total employment)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>TPE_step_aug</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>-0.1057338462188449</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.08954915781745076</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Fertilizer consumption (% of fertilizer production)</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>MLP</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Random_jitter_aug</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>-50.79741940984609</v>
+      </c>
+      <c r="E25" t="n">
+        <v>44.91033702003426</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Fertilizer consumption (% of fertilizer production)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Random_orig</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>-71.03285108098866</v>
+      </c>
+      <c r="E26" t="n">
+        <v>22.2374871443471</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Fertilizer consumption (% of fertilizer production)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Random_step_aug</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>-73.47167096624257</v>
+      </c>
+      <c r="E27" t="n">
+        <v>8.521519470986854</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Fertilizer consumption (% of fertilizer production)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>TPE_jitter_aug</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>-70.48490033635976</v>
+      </c>
+      <c r="E28" t="n">
+        <v>25.33689662365463</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Fertilizer consumption (% of fertilizer production)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>TPE_orig</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>-77.18818173894765</v>
+      </c>
+      <c r="E29" t="n">
+        <v>35.76411924524427</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Fertilizer consumption (% of fertilizer production)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>TPE_step_aug</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D30" t="n">
         <v>-61.52351270208241</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E30" t="n">
         <v>26.67707647619864</v>
       </c>
     </row>

--- a/results/errors/residuals_stats.xlsx
+++ b/results/errors/residuals_stats.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -863,10 +863,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.2976835713699069</v>
+        <v>-0.1111103043868746</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1401521899295723</v>
+        <v>0.08404276152381063</v>
       </c>
     </row>
     <row r="20">
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.2139017329528536</v>
+        <v>-0.2719437823608126</v>
       </c>
       <c r="E22" t="n">
-        <v>0.02975115557440877</v>
+        <v>0.1088925339771187</v>
       </c>
     </row>
     <row r="23">
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.03431830266263147</v>
+        <v>-0.1292892442062106</v>
       </c>
       <c r="E23" t="n">
-        <v>0.05706355353125692</v>
+        <v>0.07490727682837606</v>
       </c>
     </row>
     <row r="24">
@@ -978,10 +978,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.1057338462188449</v>
+        <v>-0.1475177750899996</v>
       </c>
       <c r="E24" t="n">
-        <v>0.08954915781745076</v>
+        <v>0.08091423292883992</v>
       </c>
     </row>
     <row r="25">
@@ -1120,6 +1120,144 @@
       </c>
       <c r="E30" t="n">
         <v>26.67707647619864</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fertilizer consumption (kilograms per hectare of arable land)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Random_jitter_aug</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>-4.869459761066946</v>
+      </c>
+      <c r="E31" t="n">
+        <v>6.422566434715526</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Fertilizer consumption (kilograms per hectare of arable land)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Random_orig</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>-3.799980525826388</v>
+      </c>
+      <c r="E32" t="n">
+        <v>6.594235480175403</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Fertilizer consumption (kilograms per hectare of arable land)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Random_step_aug</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.26748278450597</v>
+      </c>
+      <c r="E33" t="n">
+        <v>6.364604977176518</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Fertilizer consumption (kilograms per hectare of arable land)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>TPE_jitter_aug</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1.145181047038522</v>
+      </c>
+      <c r="E34" t="n">
+        <v>6.797959720231388</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Fertilizer consumption (kilograms per hectare of arable land)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>TPE_orig</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1.890134449149198</v>
+      </c>
+      <c r="E35" t="n">
+        <v>7.094508940737969</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Fertilizer consumption (kilograms per hectare of arable land)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>TPE_step_aug</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>-6.735370998238498</v>
+      </c>
+      <c r="E36" t="n">
+        <v>6.376422437431442</v>
       </c>
     </row>
   </sheetData>

--- a/results/errors/residuals_stats.xlsx
+++ b/results/errors/residuals_stats.xlsx
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-4.869459761066946</v>
+        <v>1.177987690115994</v>
       </c>
       <c r="E31" t="n">
-        <v>6.422566434715526</v>
+        <v>6.202979673140498</v>
       </c>
     </row>
     <row r="32">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-3.799980525826388</v>
+        <v>8.692584629202909</v>
       </c>
       <c r="E32" t="n">
-        <v>6.594235480175403</v>
+        <v>6.717773564639376</v>
       </c>
     </row>
     <row r="33">
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.26748278450597</v>
+        <v>-2.910887126778537</v>
       </c>
       <c r="E33" t="n">
-        <v>6.364604977176518</v>
+        <v>6.589225211502163</v>
       </c>
     </row>
     <row r="34">
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1.145181047038522</v>
+        <v>7.871682758475369</v>
       </c>
       <c r="E34" t="n">
-        <v>6.797959720231388</v>
+        <v>7.22433669058</v>
       </c>
     </row>
     <row r="35">
@@ -1231,10 +1231,10 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1.890134449149198</v>
+        <v>16.47073709502322</v>
       </c>
       <c r="E35" t="n">
-        <v>7.094508940737969</v>
+        <v>7.942099519263734</v>
       </c>
     </row>
     <row r="36">
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-6.735370998238498</v>
+        <v>-2.902496700142795</v>
       </c>
       <c r="E36" t="n">
-        <v>6.376422437431442</v>
+        <v>6.410306966646612</v>
       </c>
     </row>
   </sheetData>

--- a/results/errors/residuals_stats.xlsx
+++ b/results/errors/residuals_stats.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -992,7 +992,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MLP</t>
+          <t>CNN</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-50.79741940984609</v>
+        <v>-39.69888768682362</v>
       </c>
       <c r="E25" t="n">
-        <v>44.91033702003426</v>
+        <v>26.28651327441024</v>
       </c>
     </row>
     <row r="26">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MLP</t>
+          <t>CNN</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-71.03285108098866</v>
+        <v>-49.22014554930473</v>
       </c>
       <c r="E26" t="n">
-        <v>22.2374871443471</v>
+        <v>27.185848968657</v>
       </c>
     </row>
     <row r="27">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MLP</t>
+          <t>CNN</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-73.47167096624257</v>
+        <v>-66.45332527749484</v>
       </c>
       <c r="E27" t="n">
-        <v>8.521519470986854</v>
+        <v>25.4205307653504</v>
       </c>
     </row>
     <row r="28">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MLP</t>
+          <t>CNN</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-70.48490033635976</v>
+        <v>-57.2433956671703</v>
       </c>
       <c r="E28" t="n">
-        <v>25.33689662365463</v>
+        <v>20.52637235503885</v>
       </c>
     </row>
     <row r="29">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MLP</t>
+          <t>CNN</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-77.18818173894765</v>
+        <v>-43.96611676702382</v>
       </c>
       <c r="E29" t="n">
-        <v>35.76411924524427</v>
+        <v>21.17945634976692</v>
       </c>
     </row>
     <row r="30">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MLP</t>
+          <t>CNN</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1116,16 +1116,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-61.52351270208241</v>
+        <v>-58.74224362859609</v>
       </c>
       <c r="E30" t="n">
-        <v>26.67707647619864</v>
+        <v>25.78967328097856</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Fertilizer consumption (kilograms per hectare of arable land)</t>
+          <t>Fertilizer consumption (% of fertilizer production)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1139,16 +1139,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1.177987690115994</v>
+        <v>-50.79741940984609</v>
       </c>
       <c r="E31" t="n">
-        <v>6.202979673140498</v>
+        <v>44.91033702003426</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Fertilizer consumption (kilograms per hectare of arable land)</t>
+          <t>Fertilizer consumption (% of fertilizer production)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1162,16 +1162,16 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>8.692584629202909</v>
+        <v>-71.03285108098866</v>
       </c>
       <c r="E32" t="n">
-        <v>6.717773564639376</v>
+        <v>22.2374871443471</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Fertilizer consumption (kilograms per hectare of arable land)</t>
+          <t>Fertilizer consumption (% of fertilizer production)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1185,16 +1185,16 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-2.910887126778537</v>
+        <v>-73.47167096624257</v>
       </c>
       <c r="E33" t="n">
-        <v>6.589225211502163</v>
+        <v>8.521519470986854</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Fertilizer consumption (kilograms per hectare of arable land)</t>
+          <t>Fertilizer consumption (% of fertilizer production)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1208,16 +1208,16 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>7.871682758475369</v>
+        <v>-70.48490033635976</v>
       </c>
       <c r="E34" t="n">
-        <v>7.22433669058</v>
+        <v>25.33689662365463</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Fertilizer consumption (kilograms per hectare of arable land)</t>
+          <t>Fertilizer consumption (% of fertilizer production)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1231,33 +1231,309 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>16.47073709502322</v>
+        <v>-77.18818173894765</v>
       </c>
       <c r="E35" t="n">
-        <v>7.942099519263734</v>
+        <v>35.76411924524427</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>Fertilizer consumption (% of fertilizer production)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>TPE_step_aug</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>-61.52351270208241</v>
+      </c>
+      <c r="E36" t="n">
+        <v>26.67707647619864</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>Fertilizer consumption (kilograms per hectare of arable land)</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>MLP</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Random_jitter_aug</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1.177987690115994</v>
+      </c>
+      <c r="E37" t="n">
+        <v>6.202979673140498</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Fertilizer consumption (kilograms per hectare of arable land)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Random_orig</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>8.692584629202909</v>
+      </c>
+      <c r="E38" t="n">
+        <v>6.717773564639376</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Fertilizer consumption (kilograms per hectare of arable land)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Random_step_aug</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>-2.910887126778537</v>
+      </c>
+      <c r="E39" t="n">
+        <v>6.589225211502163</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Fertilizer consumption (kilograms per hectare of arable land)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>TPE_jitter_aug</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>7.871682758475369</v>
+      </c>
+      <c r="E40" t="n">
+        <v>7.22433669058</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Fertilizer consumption (kilograms per hectare of arable land)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>TPE_orig</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>16.47073709502322</v>
+      </c>
+      <c r="E41" t="n">
+        <v>7.942099519263734</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Fertilizer consumption (kilograms per hectare of arable land)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
         <is>
           <t>TPE_step_aug</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D42" t="n">
         <v>-2.902496700142795</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E42" t="n">
         <v>6.410306966646612</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Livestock production index (2014-2016 = 100)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CNN</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Random_jitter_aug</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>2.959673055013027</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2.280703302710028</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Livestock production index (2014-2016 = 100)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CNN</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Random_orig</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>2.217299906412767</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2.312900760700776</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Livestock production index (2014-2016 = 100)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CNN</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Random_step_aug</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>2.787704772949223</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2.922189061609219</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Livestock production index (2014-2016 = 100)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CNN</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>TPE_jitter_aug</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>2.536089070638027</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2.360900442235865</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Livestock production index (2014-2016 = 100)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CNN</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>TPE_orig</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1.835130818684902</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2.407945277614522</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Livestock production index (2014-2016 = 100)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CNN</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>TPE_step_aug</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>2.584296671549486</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2.346112209082237</v>
       </c>
     </row>
   </sheetData>

--- a/results/errors/residuals_stats.xlsx
+++ b/results/errors/residuals_stats.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Agricultural raw materials imports (% of merchandise imports)</t>
+          <t>Agricultural land (% of land area)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.1707294536750584</v>
+        <v>1.00100304211886</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06821902511075469</v>
+        <v>1.418626030692614</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Agricultural raw materials imports (% of merchandise imports)</t>
+          <t>Agricultural land (% of land area)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -495,16 +495,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.227823451471435</v>
+        <v>0.9934334709489209</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05420868590638327</v>
+        <v>1.505996643649524</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Agricultural raw materials imports (% of merchandise imports)</t>
+          <t>Agricultural land (% of land area)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -518,16 +518,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.1265317751090794</v>
+        <v>1.452720418827845</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06901538823188524</v>
+        <v>1.198683680860964</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Agricultural raw materials imports (% of merchandise imports)</t>
+          <t>Agricultural land (% of land area)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,16 +541,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.1527616931121617</v>
+        <v>-0.08470748339383505</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08065390497604527</v>
+        <v>1.028905440909389</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Agricultural raw materials imports (% of merchandise imports)</t>
+          <t>Agricultural land (% of land area)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -564,16 +564,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.1680943720659683</v>
+        <v>1.135964170353724</v>
       </c>
       <c r="E6" t="n">
-        <v>0.06200653232142157</v>
+        <v>1.397114828267005</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Agricultural raw materials imports (% of merchandise imports)</t>
+          <t>Agricultural land (% of land area)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -587,16 +587,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.347116458778962</v>
+        <v>0.4119197482112907</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08406752988752667</v>
+        <v>1.245088845379758</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Agriculture, forestry, and fishing, value added (% of GDP)</t>
+          <t>Agricultural raw materials imports (% of merchandise imports)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -610,16 +610,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.09056642912615354</v>
+        <v>-0.1707294536750584</v>
       </c>
       <c r="E8" t="n">
-        <v>0.07486015130644408</v>
+        <v>0.06821902511075469</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Agriculture, forestry, and fishing, value added (% of GDP)</t>
+          <t>Agricultural raw materials imports (% of merchandise imports)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -633,16 +633,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.09823009632814939</v>
+        <v>-0.227823451471435</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0789877133524951</v>
+        <v>0.05420868590638327</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Agriculture, forestry, and fishing, value added (% of GDP)</t>
+          <t>Agricultural raw materials imports (% of merchandise imports)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -656,16 +656,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.09950033091295774</v>
+        <v>-0.1265317751090794</v>
       </c>
       <c r="E10" t="n">
-        <v>0.07977896501188841</v>
+        <v>0.06901538823188524</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Agriculture, forestry, and fishing, value added (% of GDP)</t>
+          <t>Agricultural raw materials imports (% of merchandise imports)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -679,16 +679,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.1001670088647705</v>
+        <v>-0.1527616931121617</v>
       </c>
       <c r="E11" t="n">
-        <v>0.09099602271681395</v>
+        <v>0.08065390497604527</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Agriculture, forestry, and fishing, value added (% of GDP)</t>
+          <t>Agricultural raw materials imports (% of merchandise imports)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -698,20 +698,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TPE_step_aug</t>
+          <t>TPE_orig</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.09479353092897946</v>
+        <v>-0.1680943720659683</v>
       </c>
       <c r="E12" t="n">
-        <v>0.09064745475416747</v>
+        <v>0.06200653232142157</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cereal yield (kg per hectare)</t>
+          <t>Agricultural raw materials imports (% of merchandise imports)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -721,20 +721,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Random_jitter_aug</t>
+          <t>TPE_step_aug</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>72.55377604166642</v>
+        <v>-1.347116458778962</v>
       </c>
       <c r="E13" t="n">
-        <v>337.8101647926924</v>
+        <v>0.08406752988752667</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cereal yield (kg per hectare)</t>
+          <t>Agriculture, forestry, and fishing, value added (% of GDP)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -744,20 +744,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Random_orig</t>
+          <t>Random_jitter_aug</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-102.492797851563</v>
+        <v>0.09056642912615354</v>
       </c>
       <c r="E14" t="n">
-        <v>344.1967708716385</v>
+        <v>0.07486015130644408</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cereal yield (kg per hectare)</t>
+          <t>Agriculture, forestry, and fishing, value added (% of GDP)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -767,20 +767,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Random_step_aug</t>
+          <t>Random_orig</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-119.3868977864586</v>
+        <v>0.09823009632814939</v>
       </c>
       <c r="E15" t="n">
-        <v>352.7298430479694</v>
+        <v>0.0789877133524951</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cereal yield (kg per hectare)</t>
+          <t>Agriculture, forestry, and fishing, value added (% of GDP)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -790,20 +790,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TPE_jitter_aug</t>
+          <t>Random_step_aug</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-33.17229817708358</v>
+        <v>0.09950033091295774</v>
       </c>
       <c r="E16" t="n">
-        <v>353.036953051361</v>
+        <v>0.07977896501188841</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cereal yield (kg per hectare)</t>
+          <t>Agriculture, forestry, and fishing, value added (% of GDP)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -813,20 +813,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TPE_orig</t>
+          <t>TPE_jitter_aug</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-144.3757324218755</v>
+        <v>0.1001670088647705</v>
       </c>
       <c r="E17" t="n">
-        <v>354.4326368779683</v>
+        <v>0.09099602271681395</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cereal yield (kg per hectare)</t>
+          <t>Agriculture, forestry, and fishing, value added (% of GDP)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -840,16 +840,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-87.2544108072919</v>
+        <v>0.09479353092897946</v>
       </c>
       <c r="E18" t="n">
-        <v>354.0006234251761</v>
+        <v>0.09064745475416747</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Employment in agriculture (% of total employment)</t>
+          <t>Arable land (% of land area)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -863,16 +863,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.1111103043868746</v>
+        <v>1.463054272659733</v>
       </c>
       <c r="E19" t="n">
-        <v>0.08404276152381063</v>
+        <v>0.4319592140805991</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Employment in agriculture (% of total employment)</t>
+          <t>Arable land (% of land area)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -886,16 +886,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.1320322499587741</v>
+        <v>1.351831051834537</v>
       </c>
       <c r="E20" t="n">
-        <v>0.09499714155921102</v>
+        <v>0.4894242737187486</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Employment in agriculture (% of total employment)</t>
+          <t>Arable land (% of land area)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -909,16 +909,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.1210509286239352</v>
+        <v>0.3418617215041853</v>
       </c>
       <c r="E21" t="n">
-        <v>0.08998772879370809</v>
+        <v>0.4479615333336572</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Employment in agriculture (% of total employment)</t>
+          <t>Arable land (% of land area)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -932,16 +932,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.2719437823608126</v>
+        <v>0.807596299179508</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1088925339771187</v>
+        <v>0.5055093433707493</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Employment in agriculture (% of total employment)</t>
+          <t>Arable land (% of land area)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -955,16 +955,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.1292892442062106</v>
+        <v>0.6106472940525549</v>
       </c>
       <c r="E23" t="n">
-        <v>0.07490727682837606</v>
+        <v>0.4285389516443968</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Employment in agriculture (% of total employment)</t>
+          <t>Arable land (% of land area)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -978,21 +978,21 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.1475177750899996</v>
+        <v>1.299980732925846</v>
       </c>
       <c r="E24" t="n">
-        <v>0.08091423292883992</v>
+        <v>0.4528470973817011</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Fertilizer consumption (% of fertilizer production)</t>
+          <t>Cereal yield (kg per hectare)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CNN</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1001,21 +1001,21 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-39.69888768682362</v>
+        <v>72.55377604166642</v>
       </c>
       <c r="E25" t="n">
-        <v>26.28651327441024</v>
+        <v>337.8101647926924</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Fertilizer consumption (% of fertilizer production)</t>
+          <t>Cereal yield (kg per hectare)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CNN</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-49.22014554930473</v>
+        <v>-102.492797851563</v>
       </c>
       <c r="E26" t="n">
-        <v>27.185848968657</v>
+        <v>344.1967708716385</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Fertilizer consumption (% of fertilizer production)</t>
+          <t>Cereal yield (kg per hectare)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CNN</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1047,21 +1047,21 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-66.45332527749484</v>
+        <v>-119.3868977864586</v>
       </c>
       <c r="E27" t="n">
-        <v>25.4205307653504</v>
+        <v>352.7298430479694</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Fertilizer consumption (% of fertilizer production)</t>
+          <t>Cereal yield (kg per hectare)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CNN</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1070,21 +1070,21 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-57.2433956671703</v>
+        <v>-33.17229817708358</v>
       </c>
       <c r="E28" t="n">
-        <v>20.52637235503885</v>
+        <v>353.036953051361</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Fertilizer consumption (% of fertilizer production)</t>
+          <t>Cereal yield (kg per hectare)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CNN</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1093,21 +1093,21 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-43.96611676702382</v>
+        <v>-144.3757324218755</v>
       </c>
       <c r="E29" t="n">
-        <v>21.17945634976692</v>
+        <v>354.4326368779683</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Fertilizer consumption (% of fertilizer production)</t>
+          <t>Cereal yield (kg per hectare)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CNN</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1116,16 +1116,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-58.74224362859609</v>
+        <v>-87.2544108072919</v>
       </c>
       <c r="E30" t="n">
-        <v>25.78967328097856</v>
+        <v>354.0006234251761</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Fertilizer consumption (% of fertilizer production)</t>
+          <t>Employment in agriculture (% of total employment)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1139,16 +1139,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-50.79741940984609</v>
+        <v>-0.1111103043868746</v>
       </c>
       <c r="E31" t="n">
-        <v>44.91033702003426</v>
+        <v>0.08404276152381063</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Fertilizer consumption (% of fertilizer production)</t>
+          <t>Employment in agriculture (% of total employment)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1162,16 +1162,16 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-71.03285108098866</v>
+        <v>-0.1320322499587741</v>
       </c>
       <c r="E32" t="n">
-        <v>22.2374871443471</v>
+        <v>0.09499714155921102</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Fertilizer consumption (% of fertilizer production)</t>
+          <t>Employment in agriculture (% of total employment)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1185,16 +1185,16 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-73.47167096624257</v>
+        <v>-0.1210509286239352</v>
       </c>
       <c r="E33" t="n">
-        <v>8.521519470986854</v>
+        <v>0.08998772879370809</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Fertilizer consumption (% of fertilizer production)</t>
+          <t>Employment in agriculture (% of total employment)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1208,16 +1208,16 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-70.48490033635976</v>
+        <v>-0.2719437823608126</v>
       </c>
       <c r="E34" t="n">
-        <v>25.33689662365463</v>
+        <v>0.1088925339771187</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Fertilizer consumption (% of fertilizer production)</t>
+          <t>Employment in agriculture (% of total employment)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1231,16 +1231,16 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-77.18818173894765</v>
+        <v>-0.1292892442062106</v>
       </c>
       <c r="E35" t="n">
-        <v>35.76411924524427</v>
+        <v>0.07490727682837606</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Fertilizer consumption (% of fertilizer production)</t>
+          <t>Employment in agriculture (% of total employment)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1254,21 +1254,21 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-61.52351270208241</v>
+        <v>-0.1475177750899996</v>
       </c>
       <c r="E36" t="n">
-        <v>26.67707647619864</v>
+        <v>0.08091423292883992</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Fertilizer consumption (kilograms per hectare of arable land)</t>
+          <t>Fertilizer consumption (% of fertilizer production)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MLP</t>
+          <t>CNN</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1277,21 +1277,21 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1.177987690115994</v>
+        <v>-39.69888768682362</v>
       </c>
       <c r="E37" t="n">
-        <v>6.202979673140498</v>
+        <v>26.28651327441024</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Fertilizer consumption (kilograms per hectare of arable land)</t>
+          <t>Fertilizer consumption (% of fertilizer production)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MLP</t>
+          <t>CNN</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1300,21 +1300,21 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>8.692584629202909</v>
+        <v>-49.22014554930473</v>
       </c>
       <c r="E38" t="n">
-        <v>6.717773564639376</v>
+        <v>27.185848968657</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Fertilizer consumption (kilograms per hectare of arable land)</t>
+          <t>Fertilizer consumption (% of fertilizer production)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MLP</t>
+          <t>CNN</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1323,21 +1323,21 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-2.910887126778537</v>
+        <v>-66.45332527749484</v>
       </c>
       <c r="E39" t="n">
-        <v>6.589225211502163</v>
+        <v>25.4205307653504</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Fertilizer consumption (kilograms per hectare of arable land)</t>
+          <t>Fertilizer consumption (% of fertilizer production)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MLP</t>
+          <t>CNN</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1346,21 +1346,21 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>7.871682758475369</v>
+        <v>-57.2433956671703</v>
       </c>
       <c r="E40" t="n">
-        <v>7.22433669058</v>
+        <v>20.52637235503885</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Fertilizer consumption (kilograms per hectare of arable land)</t>
+          <t>Fertilizer consumption (% of fertilizer production)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MLP</t>
+          <t>CNN</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1369,21 +1369,21 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>16.47073709502322</v>
+        <v>-43.96611676702382</v>
       </c>
       <c r="E41" t="n">
-        <v>7.942099519263734</v>
+        <v>21.17945634976692</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Fertilizer consumption (kilograms per hectare of arable land)</t>
+          <t>Fertilizer consumption (% of fertilizer production)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MLP</t>
+          <t>CNN</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1392,21 +1392,21 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>-2.902496700142795</v>
+        <v>-58.74224362859609</v>
       </c>
       <c r="E42" t="n">
-        <v>6.410306966646612</v>
+        <v>25.78967328097856</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Livestock production index (2014-2016 = 100)</t>
+          <t>Fertilizer consumption (% of fertilizer production)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CNN</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1415,21 +1415,21 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2.959673055013027</v>
+        <v>-50.79741940984609</v>
       </c>
       <c r="E43" t="n">
-        <v>2.280703302710028</v>
+        <v>44.91033702003426</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Livestock production index (2014-2016 = 100)</t>
+          <t>Fertilizer consumption (% of fertilizer production)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CNN</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1438,21 +1438,21 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2.217299906412767</v>
+        <v>-71.03285108098866</v>
       </c>
       <c r="E44" t="n">
-        <v>2.312900760700776</v>
+        <v>22.2374871443471</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Livestock production index (2014-2016 = 100)</t>
+          <t>Fertilizer consumption (% of fertilizer production)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CNN</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1461,21 +1461,21 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.787704772949223</v>
+        <v>-73.47167096624257</v>
       </c>
       <c r="E45" t="n">
-        <v>2.922189061609219</v>
+        <v>8.521519470986854</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Livestock production index (2014-2016 = 100)</t>
+          <t>Fertilizer consumption (% of fertilizer production)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CNN</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1484,21 +1484,21 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2.536089070638027</v>
+        <v>-70.48490033635976</v>
       </c>
       <c r="E46" t="n">
-        <v>2.360900442235865</v>
+        <v>25.33689662365463</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Livestock production index (2014-2016 = 100)</t>
+          <t>Fertilizer consumption (% of fertilizer production)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CNN</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1507,32 +1507,308 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1.835130818684902</v>
+        <v>-77.18818173894765</v>
       </c>
       <c r="E47" t="n">
-        <v>2.407945277614522</v>
+        <v>35.76411924524427</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>Fertilizer consumption (% of fertilizer production)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>TPE_step_aug</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>-61.52351270208241</v>
+      </c>
+      <c r="E48" t="n">
+        <v>26.67707647619864</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Fertilizer consumption (kilograms per hectare of arable land)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Random_jitter_aug</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1.177987690115994</v>
+      </c>
+      <c r="E49" t="n">
+        <v>6.202979673140498</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Fertilizer consumption (kilograms per hectare of arable land)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Random_orig</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>8.692584629202909</v>
+      </c>
+      <c r="E50" t="n">
+        <v>6.717773564639376</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Fertilizer consumption (kilograms per hectare of arable land)</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Random_step_aug</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>-2.910887126778537</v>
+      </c>
+      <c r="E51" t="n">
+        <v>6.589225211502163</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Fertilizer consumption (kilograms per hectare of arable land)</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>TPE_jitter_aug</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>7.871682758475369</v>
+      </c>
+      <c r="E52" t="n">
+        <v>7.22433669058</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Fertilizer consumption (kilograms per hectare of arable land)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>TPE_orig</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>16.47073709502322</v>
+      </c>
+      <c r="E53" t="n">
+        <v>7.942099519263734</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Fertilizer consumption (kilograms per hectare of arable land)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>TPE_step_aug</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>-2.902496700142795</v>
+      </c>
+      <c r="E54" t="n">
+        <v>6.410306966646612</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>Livestock production index (2014-2016 = 100)</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>CNN</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Random_jitter_aug</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>2.959673055013027</v>
+      </c>
+      <c r="E55" t="n">
+        <v>2.280703302710028</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Livestock production index (2014-2016 = 100)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>CNN</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Random_orig</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>2.217299906412767</v>
+      </c>
+      <c r="E56" t="n">
+        <v>2.312900760700776</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Livestock production index (2014-2016 = 100)</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CNN</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Random_step_aug</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>2.787704772949223</v>
+      </c>
+      <c r="E57" t="n">
+        <v>2.922189061609219</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Livestock production index (2014-2016 = 100)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CNN</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>TPE_jitter_aug</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>2.536089070638027</v>
+      </c>
+      <c r="E58" t="n">
+        <v>2.360900442235865</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Livestock production index (2014-2016 = 100)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CNN</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>TPE_orig</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1.835130818684902</v>
+      </c>
+      <c r="E59" t="n">
+        <v>2.407945277614522</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Livestock production index (2014-2016 = 100)</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>CNN</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
         <is>
           <t>TPE_step_aug</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="D60" t="n">
         <v>2.584296671549486</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E60" t="n">
         <v>2.346112209082237</v>
       </c>
     </row>
